--- a/files/港岛-北角-海璇 II.xlsx
+++ b/files/港岛-北角-海璇 II.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6709,1463 +6575,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海璇 II - 3A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>93 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>93 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 755呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 412呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 718呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 359呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 376呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 368呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海璇 II - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>30 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>30 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 2080呎 (4+房)
-$12,000万
-$57,692/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 2073呎 (4+房)
-$12,173万
-$58,721/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$7,162万
-$49,459/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$5,500万
-$49,505/呎
-(25年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5,636万
-$38,925/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4,389万
-$39,505/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5,431万
-$37,506/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4,536万
-$40,830/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1492呎 (4+房)
-$5,939万
-$39,805/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1155呎 (3房)
-$4,572万
-$39,586/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5,200万
-$35,912/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4,538万
-$40,846/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5,148万
-$35,552/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4,307万
-$38,765/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5,230万
-$36,119/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4,100万
-$36,906/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$4,987万
-$34,439/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4,166万
-$37,496/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5,153万
-$35,586/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$3,962万
-$35,658/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$4,819万
-$33,281/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$3,904万
-$35,139/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$4,780万
-$33,011/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$3,869万
-$34,827/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5,168万
-$35,691/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$3,765万
-$33,891/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$4,940万
-$34,116/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$3,825万
-$34,432/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-$4,649万
-$32,468/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1095呎 (3房)
-$4,278万
-$39,068/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-北角-海璇 II.xlsx
+++ b/files/港岛-北角-海璇 II.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +137,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +218,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -6575,4 +6746,1463 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 755呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 412呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 718呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 359呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 376呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 368呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 2080呎 (4+房)
+$12000万
+$57,692/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2073呎 (4+房)
+$12173万
+$58,721/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$7162万
+$49,459/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$5500万
+$49,505/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5636万
+$38,925/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4389万
+$39,505/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5431万
+$37,506/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4536万
+$40,830/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1492呎 (4+房)
+$5939万
+$39,805/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1155呎 (3房)
+$4572万
+$39,586/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5200万
+$35,912/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4538万
+$40,846/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5148万
+$35,552/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4307万
+$38,765/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5230万
+$36,119/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4100万
+$36,906/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$4987万
+$34,439/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4166万
+$37,496/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5153万
+$35,586/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$3962万
+$35,658/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$4819万
+$33,281/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$3904万
+$35,139/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$4780万
+$33,011/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$3869万
+$34,827/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5168万
+$35,691/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$3765万
+$33,891/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$4940万
+$34,116/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$3825万
+$34,432/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+$4649万
+$32,468/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1095呎 (3房)
+$4278万
+$39,068/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-北角-海璇 II.xlsx
+++ b/files/港岛-北角-海璇 II.xlsx
@@ -645,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-北角-海璇 II.xlsx
+++ b/files/港岛-北角-海璇 II.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:N125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -648,6 +648,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -705,6 +709,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -755,6 +779,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -805,6 +849,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -855,6 +919,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -905,6 +989,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -955,6 +1059,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1005,6 +1129,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1055,6 +1199,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1105,6 +1269,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1155,6 +1339,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1205,6 +1409,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1255,6 +1479,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1305,6 +1549,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1355,6 +1619,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1405,6 +1689,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1455,6 +1759,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1505,6 +1829,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1555,6 +1899,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1605,6 +1969,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1655,6 +2039,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1705,6 +2109,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1755,6 +2179,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1805,6 +2249,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1855,6 +2319,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1905,6 +2389,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1955,6 +2459,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2005,6 +2529,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2055,6 +2599,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2105,6 +2669,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2155,6 +2739,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2205,6 +2809,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2255,6 +2879,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2305,6 +2949,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2355,6 +3019,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2405,6 +3089,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2455,6 +3159,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2505,6 +3229,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2555,6 +3299,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2605,6 +3369,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2655,6 +3439,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2705,6 +3509,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2755,6 +3579,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2805,6 +3649,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2855,6 +3719,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2905,6 +3789,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2955,6 +3859,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3005,6 +3929,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3055,6 +3999,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3105,6 +4069,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3155,6 +4139,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3205,6 +4209,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3255,6 +4279,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3305,6 +4349,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3355,6 +4419,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3405,6 +4489,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3455,6 +4559,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3505,6 +4629,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3555,6 +4699,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3605,6 +4769,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3655,6 +4839,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3705,6 +4909,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3755,6 +4979,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3805,6 +5049,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3855,6 +5119,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3905,6 +5189,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3955,6 +5259,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4005,6 +5329,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4055,6 +5399,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4105,6 +5469,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4155,6 +5539,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4205,6 +5609,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4255,6 +5679,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4305,6 +5749,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4355,6 +5819,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4405,6 +5889,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4455,6 +5959,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4505,6 +6029,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4555,6 +6099,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4605,6 +6169,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4655,6 +6239,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4705,6 +6309,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4755,6 +6379,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4805,6 +6449,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4855,6 +6519,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4905,6 +6589,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4955,6 +6659,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5005,6 +6729,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5055,6 +6799,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5105,6 +6869,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5155,6 +6939,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5205,6 +7009,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5255,6 +7079,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5305,6 +7149,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5355,6 +7219,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5401,6 +7285,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5447,6 +7351,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5493,6 +7417,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5539,6 +7483,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5585,6 +7549,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5631,6 +7615,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5677,6 +7681,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5723,6 +7747,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5769,6 +7813,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5815,6 +7879,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5861,6 +7945,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5907,6 +8011,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5953,6 +8077,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5999,6 +8143,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6045,6 +8209,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6091,6 +8275,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6137,6 +8341,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6183,6 +8407,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6229,6 +8473,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6275,6 +8539,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6321,6 +8605,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6367,6 +8671,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6413,6 +8737,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6459,6 +8803,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6505,6 +8869,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6551,6 +8935,26 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6597,6 +9001,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6643,6 +9067,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6689,6 +9133,26 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6735,13 +9199,33 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -7855,7 +10339,7 @@
           <t>A | 2080呎 (4+房)
 $12000万
 $57,692/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -7871,7 +10355,7 @@
           <t>A | 2073呎 (4+房)
 $12173万
 $58,721/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -7887,7 +10371,7 @@
           <t>A | 1448呎 (4+房)
 $7162万
 $49,459/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -7895,7 +10379,7 @@
           <t>B | 1111呎 (3房)
 $5500万
 $49,505/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -7910,7 +10394,7 @@
           <t>A | 1448呎 (4+房)
 $5636万
 $38,925/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -7918,7 +10402,7 @@
           <t>B | 1111呎 (3房)
 $4389万
 $39,505/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -7933,7 +10417,7 @@
           <t>A | 1448呎 (4+房)
 $5431万
 $37,506/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -7941,7 +10425,7 @@
           <t>B | 1111呎 (3房)
 $4536万
 $40,830/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
     </row>
@@ -7956,7 +10440,7 @@
           <t>A | 1492呎 (4+房)
 $5939万
 $39,805/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -7964,7 +10448,7 @@
           <t>B | 1155呎 (3房)
 $4572万
 $39,586/呎
-(24年-10月)</t>
+(24年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -7979,7 +10463,7 @@
           <t>A | 1448呎 (4+房)
 $5200万
 $35,912/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -7987,7 +10471,7 @@
           <t>B | 1111呎 (3房)
 $4538万
 $40,846/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -8002,7 +10486,7 @@
           <t>A | 1448呎 (4+房)
 $5148万
 $35,552/呎
-(24年-09月)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -8010,7 +10494,7 @@
           <t>B | 1111呎 (3房)
 $4307万
 $38,765/呎
-(24年-09月)</t>
+(24年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -8025,7 +10509,7 @@
           <t>A | 1448呎 (4+房)
 $5230万
 $36,119/呎
-(24年-10月)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -8033,7 +10517,7 @@
           <t>B | 1111呎 (3房)
 $4100万
 $36,906/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
     </row>
@@ -8048,7 +10532,7 @@
           <t>A | 1448呎 (4+房)
 $4987万
 $34,439/呎
-(24年-09月)</t>
+(24年-09月-18日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -8056,7 +10540,7 @@
           <t>B | 1111呎 (3房)
 $4166万
 $37,496/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -8071,7 +10555,7 @@
           <t>A | 1448呎 (4+房)
 $5153万
 $35,586/呎
-(24年-10月)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -8079,7 +10563,7 @@
           <t>B | 1111呎 (3房)
 $3962万
 $35,658/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -8094,7 +10578,7 @@
           <t>A | 1448呎 (4+房)
 $4819万
 $33,281/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -8102,7 +10586,7 @@
           <t>B | 1111呎 (3房)
 $3904万
 $35,139/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -8117,7 +10601,7 @@
           <t>A | 1448呎 (4+房)
 $4780万
 $33,011/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -8125,7 +10609,7 @@
           <t>B | 1111呎 (3房)
 $3869万
 $34,827/呎
-(24年-09月)</t>
+(24年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -8140,7 +10624,7 @@
           <t>A | 1448呎 (4+房)
 $5168万
 $35,691/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -8148,7 +10632,7 @@
           <t>B | 1111呎 (3房)
 $3765万
 $33,891/呎
-(24年-09月)</t>
+(24年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -8163,7 +10647,7 @@
           <t>A | 1448呎 (4+房)
 $4940万
 $34,116/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -8171,7 +10655,7 @@
           <t>B | 1111呎 (3房)
 $3825万
 $34,432/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
     </row>
@@ -8186,7 +10670,7 @@
           <t>A | 1432呎 (4+房)
 $4649万
 $32,468/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -8194,7 +10678,7 @@
           <t>B | 1095呎 (3房)
 $4278万
 $39,068/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-北角-海璇 II.xlsx
+++ b/files/港岛-北角-海璇 II.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,10 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0"/>
-  </numFmts>
-  <fonts count="19">
+  <numFmts count="0"/>
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,11 +117,6 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -202,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -214,9 +206,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -265,9 +254,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -635,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N125"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -644,8 +630,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -7238,1986 +7224,6 @@
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="n">
-        <v>2080</v>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>120000000</v>
-      </c>
-      <c r="I96" s="5" t="n">
-        <v>57692</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L96" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M96" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N96" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="n">
-        <v>2073</v>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="n">
-        <v>121728096</v>
-      </c>
-      <c r="I97" s="5" t="n">
-        <v>58721</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>55000000</v>
-      </c>
-      <c r="I98" s="5" t="n">
-        <v>49505</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L98" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N98" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="n">
-        <v>71616000</v>
-      </c>
-      <c r="I99" s="5" t="n">
-        <v>49459</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M99" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>43890000</v>
-      </c>
-      <c r="I100" s="5" t="n">
-        <v>39505</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N100" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>56364000</v>
-      </c>
-      <c r="I101" s="5" t="n">
-        <v>38925</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N101" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>45362000</v>
-      </c>
-      <c r="I102" s="5" t="n">
-        <v>40830</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N102" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>54308800</v>
-      </c>
-      <c r="I103" s="5" t="n">
-        <v>37506</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="n">
-        <v>1155</v>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>45721830</v>
-      </c>
-      <c r="I104" s="5" t="n">
-        <v>39586</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M104" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N104" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="n">
-        <v>1492</v>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>59388800</v>
-      </c>
-      <c r="I105" s="5" t="n">
-        <v>39805</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M105" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N105" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="H106" s="5" t="n">
-        <v>45380000</v>
-      </c>
-      <c r="I106" s="5" t="n">
-        <v>40846</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M106" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N106" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="H107" s="5" t="n">
-        <v>52000000</v>
-      </c>
-      <c r="I107" s="5" t="n">
-        <v>35912</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M107" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N107" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="n">
-        <v>43067640</v>
-      </c>
-      <c r="I108" s="5" t="n">
-        <v>38765</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M108" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N108" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="n">
-        <v>51479000</v>
-      </c>
-      <c r="I109" s="5" t="n">
-        <v>35552</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K109" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L109" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M109" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N109" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="H110" s="5" t="n">
-        <v>41002500</v>
-      </c>
-      <c r="I110" s="5" t="n">
-        <v>36906</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M110" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N110" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="n">
-        <v>52300000</v>
-      </c>
-      <c r="I111" s="5" t="n">
-        <v>36119</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M111" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N111" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="H112" s="5" t="n">
-        <v>41658500</v>
-      </c>
-      <c r="I112" s="5" t="n">
-        <v>37496</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M112" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N112" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>49868000</v>
-      </c>
-      <c r="I113" s="5" t="n">
-        <v>34439</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M113" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N113" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E114" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="n">
-        <v>39616500</v>
-      </c>
-      <c r="I114" s="5" t="n">
-        <v>35658</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K114" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L114" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M114" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N114" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="n">
-        <v>51528000</v>
-      </c>
-      <c r="I115" s="5" t="n">
-        <v>35586</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M115" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N115" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="n">
-        <v>39039000</v>
-      </c>
-      <c r="I116" s="5" t="n">
-        <v>35139</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M116" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N116" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="n">
-        <v>48191600</v>
-      </c>
-      <c r="I117" s="5" t="n">
-        <v>33281</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M117" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N117" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-15</t>
-        </is>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>38692500</v>
-      </c>
-      <c r="I118" s="5" t="n">
-        <v>34827</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M118" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N118" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="n">
-        <v>47800000</v>
-      </c>
-      <c r="I119" s="5" t="n">
-        <v>33011</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M119" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N119" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="n">
-        <v>37653000</v>
-      </c>
-      <c r="I120" s="5" t="n">
-        <v>33891</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M120" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N120" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="n">
-        <v>51680000</v>
-      </c>
-      <c r="I121" s="5" t="n">
-        <v>35691</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M121" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N121" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="H122" s="5" t="n">
-        <v>38253600</v>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>34432</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M122" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N122" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="n">
-        <v>49400000</v>
-      </c>
-      <c r="I123" s="5" t="n">
-        <v>34116</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M123" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N123" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>1095</v>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="H124" s="5" t="n">
-        <v>42780000</v>
-      </c>
-      <c r="I124" s="5" t="n">
-        <v>39068</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M124" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N124" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="n">
-        <v>1432</v>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="n">
-        <v>46494000</v>
-      </c>
-      <c r="I125" s="5" t="n">
-        <v>32468</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M125" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N125" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -9251,120 +7257,120 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>3A座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>A | 755呎 (2房)
 -
@@ -9372,9 +7378,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>D | 412呎 (1房)
 -
@@ -9382,7 +7388,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9390,7 +7396,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9400,12 +7406,12 @@
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -9413,7 +7419,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>B | 718呎 (2房)
 -
@@ -9421,8 +7427,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -9430,7 +7436,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9438,7 +7444,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9448,12 +7454,12 @@
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -9461,7 +7467,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -9469,7 +7475,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -9477,7 +7483,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -9485,7 +7491,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9493,7 +7499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9503,12 +7509,12 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -9516,7 +7522,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -9524,7 +7530,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -9532,7 +7538,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -9540,7 +7546,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9548,7 +7554,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9558,12 +7564,12 @@
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -9571,7 +7577,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -9579,7 +7585,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -9587,7 +7593,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -9595,7 +7601,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9603,7 +7609,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9613,12 +7619,12 @@
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -9626,7 +7632,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -9634,7 +7640,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -9642,7 +7648,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -9650,7 +7656,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9658,7 +7664,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9668,12 +7674,12 @@
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -9681,7 +7687,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -9689,7 +7695,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -9697,7 +7703,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -9705,7 +7711,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9713,7 +7719,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9723,12 +7729,12 @@
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -9736,7 +7742,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -9744,7 +7750,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -9752,7 +7758,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -9760,7 +7766,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9768,7 +7774,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9778,12 +7784,12 @@
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -9791,7 +7797,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -9799,7 +7805,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -9807,7 +7813,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -9815,7 +7821,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9823,7 +7829,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9833,12 +7839,12 @@
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -9846,7 +7852,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -9854,7 +7860,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -9862,7 +7868,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -9870,7 +7876,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9878,7 +7884,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9888,12 +7894,12 @@
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -9901,7 +7907,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -9909,7 +7915,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -9917,7 +7923,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -9925,7 +7931,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9933,7 +7939,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9943,12 +7949,12 @@
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -9956,7 +7962,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -9964,7 +7970,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -9972,7 +7978,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -9980,7 +7986,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -9988,7 +7994,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -9998,12 +8004,12 @@
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -10011,7 +8017,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -10019,7 +8025,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -10027,7 +8033,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -10035,7 +8041,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -10043,7 +8049,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -10053,12 +8059,12 @@
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -10066,7 +8072,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -10074,7 +8080,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -10082,7 +8088,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -10090,7 +8096,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -10098,7 +8104,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -10108,12 +8114,12 @@
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -10121,7 +8127,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -10129,7 +8135,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -10137,7 +8143,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -10145,7 +8151,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -10153,7 +8159,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -10163,12 +8169,12 @@
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -10176,7 +8182,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -10184,7 +8190,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -10192,7 +8198,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -10200,7 +8206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -10208,477 +8214,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
 -
 (待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>A | 2080呎 (4+房)
-$12000万
-$57,692/呎
-(24年-11月-24日)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>A | 2073呎 (4+房)
-$12173万
-$58,721/呎
-(24年-11月-07日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$7162万
-$49,459/呎
-(25年-12月-02日)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$5500万
-$49,505/呎
-(25年-05月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5636万
-$38,925/呎
-(24年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4389万
-$39,505/呎
-(24年-10月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5431万
-$37,506/呎
-(24年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4536万
-$40,830/呎
-(24年-10月-07日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>A | 1492呎 (4+房)
-$5939万
-$39,805/呎
-(24年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>B | 1155呎 (3房)
-$4572万
-$39,586/呎
-(24年-10月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5200万
-$35,912/呎
-(24年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4538万
-$40,846/呎
-(24年-10月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5148万
-$35,552/呎
-(24年-09月-23日)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4307万
-$38,765/呎
-(24年-09月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5230万
-$36,119/呎
-(24年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4100万
-$36,906/呎
-(24年-10月-07日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$4987万
-$34,439/呎
-(24年-09月-18日)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$4166万
-$37,496/呎
-(24年-09月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5153万
-$35,586/呎
-(24年-10月-17日)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$3962万
-$35,658/呎
-(24年-10月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$4819万
-$33,281/呎
-(24年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$3904万
-$35,139/呎
-(24年-09月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$4780万
-$33,011/呎
-(24年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$3869万
-$34,827/呎
-(24年-09月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$5168万
-$35,691/呎
-(24年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$3765万
-$33,891/呎
-(24年-09月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>A | 1448呎 (4+房)
-$4940万
-$34,116/呎
-(24年-10月-20日)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>B | 1111呎 (3房)
-$3825万
-$34,432/呎
-(24年-09月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-$4649万
-$32,468/呎
-(25年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>B | 1095呎 (3房)
-$4278万
-$39,068/呎
-(24年-11月-17日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-北角-海璇 II.xlsx
+++ b/files/港岛-北角-海璇 II.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="18">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,6 +120,11 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -194,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -206,6 +214,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -254,6 +265,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -621,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:N125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -630,8 +644,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -7224,6 +7238,1986 @@
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>2080</v>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>57692</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>2073</v>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>121728096</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>58721</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>49505</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>71616000</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>49459</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>43890000</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>39505</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>56364000</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>38925</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>45362000</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>40830</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>54308800</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>37506</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>1155</v>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>45721830</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>39586</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>1492</v>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>59388800</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>39805</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>45380000</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>40846</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>35912</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>43067640</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>38765</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>51479000</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>35552</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>41002500</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>36906</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>52300000</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>36119</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>41658500</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>37496</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>49868000</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>34439</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>39616500</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>35658</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>51528000</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>35586</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>39039000</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>35139</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>48191600</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>33281</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>38692500</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>34827</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>47800000</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>33011</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>37653000</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>33891</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>51680000</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>35691</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>38253600</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>34432</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>49400000</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>34116</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>42780000</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>39068</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>1432</v>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>46494000</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>32468</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -7257,120 +9251,120 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>3A座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 755呎 (2房)
 -
@@ -7378,9 +9372,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 412呎 (1房)
 -
@@ -7388,7 +9382,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7396,7 +9390,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -7406,12 +9400,12 @@
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -7419,7 +9413,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 718呎 (2房)
 -
@@ -7427,8 +9421,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -7436,7 +9430,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7444,7 +9438,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -7454,12 +9448,12 @@
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -7467,7 +9461,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -7475,7 +9469,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -7483,7 +9477,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -7491,7 +9485,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7499,7 +9493,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -7509,12 +9503,12 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -7522,7 +9516,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -7530,7 +9524,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -7538,7 +9532,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -7546,7 +9540,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7554,7 +9548,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -7564,12 +9558,12 @@
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -7577,7 +9571,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -7585,7 +9579,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -7593,7 +9587,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -7601,7 +9595,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7609,7 +9603,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -7619,12 +9613,12 @@
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -7632,7 +9626,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -7640,7 +9634,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -7648,7 +9642,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -7656,7 +9650,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7664,7 +9658,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -7674,12 +9668,12 @@
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -7687,7 +9681,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -7695,7 +9689,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -7703,7 +9697,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -7711,7 +9705,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7719,7 +9713,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -7729,12 +9723,12 @@
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -7742,7 +9736,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -7750,7 +9744,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -7758,7 +9752,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -7766,7 +9760,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7774,7 +9768,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -7784,12 +9778,12 @@
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -7797,7 +9791,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -7805,7 +9799,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -7813,7 +9807,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -7821,7 +9815,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7829,7 +9823,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -7839,12 +9833,12 @@
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -7852,7 +9846,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -7860,7 +9854,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -7868,7 +9862,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -7876,7 +9870,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7884,7 +9878,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -7894,12 +9888,12 @@
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -7907,7 +9901,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -7915,7 +9909,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -7923,7 +9917,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -7931,7 +9925,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7939,7 +9933,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -7949,12 +9943,12 @@
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -7962,7 +9956,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -7970,7 +9964,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -7978,7 +9972,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -7986,7 +9980,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -7994,7 +9988,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -8004,12 +9998,12 @@
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -8017,7 +10011,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -8025,7 +10019,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -8033,7 +10027,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -8041,7 +10035,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -8049,7 +10043,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -8059,12 +10053,12 @@
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -8072,7 +10066,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -8080,7 +10074,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -8088,7 +10082,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -8096,7 +10090,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -8104,7 +10098,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -8114,12 +10108,12 @@
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -8127,7 +10121,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -8135,7 +10129,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -8143,7 +10137,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -8151,7 +10145,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -8159,7 +10153,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
@@ -8169,12 +10163,12 @@
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 359呎 (1房)
 -
@@ -8182,7 +10176,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (1房)
 -
@@ -8190,7 +10184,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 507呎 (2房)
 -
@@ -8198,7 +10192,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 376呎 (1房)
 -
@@ -8206,7 +10200,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 368呎 (1房)
 -
@@ -8214,12 +10208,477 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 277呎 (开放式)
 -
 -
 (待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 2080呎 (4+房)
+$12000万
+$57,692/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2073呎 (4+房)
+$12173万
+$58,721/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$7162万
+$49,459/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$5500万
+$49,505/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5636万
+$38,925/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4389万
+$39,505/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5431万
+$37,506/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4536万
+$40,830/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1492呎 (4+房)
+$5939万
+$39,805/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1155呎 (3房)
+$4572万
+$39,586/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5200万
+$35,912/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4538万
+$40,846/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5148万
+$35,552/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4307万
+$38,765/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5230万
+$36,119/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4100万
+$36,906/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$4987万
+$34,439/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$4166万
+$37,496/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5153万
+$35,586/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$3962万
+$35,658/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$4819万
+$33,281/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$3904万
+$35,139/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$4780万
+$33,011/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$3869万
+$34,827/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$5168万
+$35,691/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$3765万
+$33,891/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1448呎 (4+房)
+$4940万
+$34,116/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1111呎 (3房)
+$3825万
+$34,432/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+$4649万
+$32,468/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1095呎 (3房)
+$4278万
+$39,068/呎
+(24年-11月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-北角-海璇 II.xlsx
+++ b/files/港岛-北角-海璇 II.xlsx
@@ -10339,7 +10339,7 @@
           <t>A | 2080呎 (4+房)
 $12000万
 $57,692/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -10355,7 +10355,7 @@
           <t>A | 2073呎 (4+房)
 $12173万
 $58,721/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -10371,7 +10371,7 @@
           <t>A | 1448呎 (4+房)
 $7162万
 $49,459/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -10379,7 +10379,7 @@
           <t>B | 1111呎 (3房)
 $5500万
 $49,505/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
           <t>A | 1448呎 (4+房)
 $5636万
 $38,925/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -10402,7 +10402,7 @@
           <t>B | 1111呎 (3房)
 $4389万
 $39,505/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
           <t>A | 1448呎 (4+房)
 $5431万
 $37,506/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -10425,7 +10425,7 @@
           <t>B | 1111呎 (3房)
 $4536万
 $40,830/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
           <t>A | 1492呎 (4+房)
 $5939万
 $39,805/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -10448,7 +10448,7 @@
           <t>B | 1155呎 (3房)
 $4572万
 $39,586/呎
-(24年-10月)</t>
+(24年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10463,7 @@
           <t>A | 1448呎 (4+房)
 $5200万
 $35,912/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -10471,7 +10471,7 @@
           <t>B | 1111呎 (3房)
 $4538万
 $40,846/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
           <t>A | 1448呎 (4+房)
 $5148万
 $35,552/呎
-(24年-09月)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -10494,7 +10494,7 @@
           <t>B | 1111呎 (3房)
 $4307万
 $38,765/呎
-(24年-09月)</t>
+(24年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
           <t>A | 1448呎 (4+房)
 $5230万
 $36,119/呎
-(24年-10月)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -10517,7 +10517,7 @@
           <t>B | 1111呎 (3房)
 $4100万
 $36,906/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
           <t>A | 1448呎 (4+房)
 $4987万
 $34,439/呎
-(24年-09月)</t>
+(24年-09月-18日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -10540,7 +10540,7 @@
           <t>B | 1111呎 (3房)
 $4166万
 $37,496/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -10555,7 +10555,7 @@
           <t>A | 1448呎 (4+房)
 $5153万
 $35,586/呎
-(24年-10月)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -10563,7 +10563,7 @@
           <t>B | 1111呎 (3房)
 $3962万
 $35,658/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10578,7 @@
           <t>A | 1448呎 (4+房)
 $4819万
 $33,281/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -10586,7 +10586,7 @@
           <t>B | 1111呎 (3房)
 $3904万
 $35,139/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
           <t>A | 1448呎 (4+房)
 $4780万
 $33,011/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -10609,7 +10609,7 @@
           <t>B | 1111呎 (3房)
 $3869万
 $34,827/呎
-(24年-09月)</t>
+(24年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
           <t>A | 1448呎 (4+房)
 $5168万
 $35,691/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -10632,7 +10632,7 @@
           <t>B | 1111呎 (3房)
 $3765万
 $33,891/呎
-(24年-09月)</t>
+(24年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -10647,7 +10647,7 @@
           <t>A | 1448呎 (4+房)
 $4940万
 $34,116/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -10655,7 +10655,7 @@
           <t>B | 1111呎 (3房)
 $3825万
 $34,432/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
           <t>A | 1432呎 (4+房)
 $4649万
 $32,468/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -10678,7 +10678,7 @@
           <t>B | 1095呎 (3房)
 $4278万
 $39,068/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
     </row>
